--- a/preguntas.xlsx
+++ b/preguntas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app 1.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555AF2AA-440D-4282-AC89-3112BB3CE452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D391DA-66A6-40EC-8843-A8C6FE52AEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6D91FCCA-5E0A-4D09-BD20-3C3DC9828942}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="141">
   <si>
     <t>id_estimulo</t>
   </si>
@@ -421,23 +421,61 @@
     <t>Recuerda que en la tabla del 7 los números aumentan sumando 7 cada vez.</t>
   </si>
   <si>
+    <t>Observa la secuencia:
+7, 14, 21, 28, 🐱, 42
+¿Qué número representa 🐱?</t>
+  </si>
+  <si>
+    <t>¡Correcto! Porque 7 × 9 = 63</t>
+  </si>
+  <si>
+    <t>Piensa qué número multiplicado por 7 da como resultado 63.</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 8 × 3 es 24.</t>
+  </si>
+  <si>
+    <t>formato_pregunta</t>
+  </si>
+  <si>
+    <t>opción múltiple</t>
+  </si>
+  <si>
+    <t>numérico</t>
+  </si>
+  <si>
+    <t>¿Cuánto es 5 × 6?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 5 × 6 es 30.</t>
+  </si>
+  <si>
+    <t>Recuerda que la tabla del 6 avanza de 6 en 6: 6, 12, 18, 24, 30...</t>
+  </si>
+  <si>
+    <t>¿Cuánto es 4 × 6?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 4 × 6 es 24.</t>
+  </si>
+  <si>
+    <t>Recuerda que la tabla del 6 avanza de 6 en 6: 6, 12, 18, 24,...</t>
+  </si>
+  <si>
     <t>Pregunta:
 7 × 😀 = 63
 ¿Qué número representa 😀?</t>
   </si>
   <si>
-    <t>Observa la secuencia:
-7, 14, 21, 28, 🐱, 42
-¿Qué número representa 🐱?</t>
-  </si>
-  <si>
-    <t>¡Correcto! Porque 7 × 9 = 63</t>
-  </si>
-  <si>
-    <t>Piensa qué número multiplicado por 7 da como resultado 63.</t>
-  </si>
-  <si>
-    <t>¡Muy bien! 8 × 3 es 24.</t>
+    <t>Pregunta:
+🦁 × 6   = 42
+¿Qué número representa 🦁?</t>
+  </si>
+  <si>
+    <t>¡Correcto! Porque 7 × 6 = 42</t>
+  </si>
+  <si>
+    <t>Piensa qué número multiplicado por 6 da como resultado 42.</t>
   </si>
 </sst>
 </file>
@@ -825,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3D7AE0-F17D-4647-96C4-DA9C95D5956E}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -833,18 +871,19 @@
     <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="68.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -864,37 +903,40 @@
         <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="135" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -910,38 +952,41 @@
       <c r="E2" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>60</v>
       </c>
-      <c r="P2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -958,37 +1003,40 @@
         <v>92</v>
       </c>
       <c r="G3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>45</v>
       </c>
-      <c r="P3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+      <c r="Q3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1005,37 +1053,40 @@
         <v>93</v>
       </c>
       <c r="G4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
       <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>14</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>18</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="O4">
-        <v>15</v>
-      </c>
       <c r="P4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1052,37 +1103,40 @@
         <v>93</v>
       </c>
       <c r="G5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" t="s">
         <v>114</v>
       </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
       <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>14</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>18</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>82</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="O5">
-        <v>15</v>
-      </c>
       <c r="P5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1099,37 +1153,40 @@
         <v>93</v>
       </c>
       <c r="G6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H6" t="s">
         <v>33</v>
       </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
       <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>14</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>18</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>34</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="O6">
-        <v>15</v>
-      </c>
       <c r="P6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1146,37 +1203,40 @@
         <v>93</v>
       </c>
       <c r="G7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" t="s">
         <v>37</v>
       </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
       <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
         <v>14</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>16</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>18</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>20</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O7">
-        <v>15</v>
-      </c>
       <c r="P7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1193,37 +1253,40 @@
         <v>93</v>
       </c>
       <c r="G8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" t="s">
         <v>117</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>18</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>24</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>38</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>83</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>28</v>
       </c>
-      <c r="M8" t="s">
-        <v>128</v>
-      </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" t="s">
+        <v>127</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="O8">
-        <v>15</v>
-      </c>
       <c r="P8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1239,38 +1302,41 @@
       <c r="E9" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>56</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>64</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>72</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>88</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>28</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>120</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="O9">
-        <v>15</v>
-      </c>
       <c r="P9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1287,37 +1353,40 @@
         <v>93</v>
       </c>
       <c r="G10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" t="s">
         <v>40</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>42</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>48</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>54</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>56</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>28</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>41</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O10">
-        <v>15</v>
-      </c>
       <c r="P10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1334,37 +1403,40 @@
         <v>93</v>
       </c>
       <c r="G11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" t="s">
         <v>43</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>48</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>54</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>56</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>63</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>20</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="O11">
-        <v>15</v>
-      </c>
       <c r="P11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1380,38 +1452,41 @@
       <c r="E12" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12">
+      <c r="G12" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I12">
         <v>30</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>35</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>36</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>39</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>28</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>122</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="O12">
-        <v>15</v>
-      </c>
       <c r="P12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1427,38 +1502,41 @@
       <c r="E13" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13">
+      <c r="G13" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13">
         <v>6</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>7</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>8</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>9</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>82</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
+        <v>125</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="N13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="O13">
-        <v>15</v>
-      </c>
       <c r="P13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1475,37 +1553,40 @@
         <v>93</v>
       </c>
       <c r="G14" t="s">
+        <v>129</v>
+      </c>
+      <c r="H14" t="s">
         <v>46</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>32</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>36</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>40</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>45</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>28</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>47</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O14">
-        <v>15</v>
-      </c>
       <c r="P14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1522,37 +1603,40 @@
         <v>96</v>
       </c>
       <c r="G15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" t="s">
         <v>49</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>50</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>51</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>52</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>53</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>28</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O15">
-        <v>15</v>
-      </c>
       <c r="P15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1569,37 +1653,40 @@
         <v>97</v>
       </c>
       <c r="G16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" t="s">
         <v>56</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>57</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>58</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>59</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>60</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>34</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O16">
-        <v>15</v>
-      </c>
       <c r="P16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1616,37 +1703,40 @@
         <v>90</v>
       </c>
       <c r="G17" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" t="s">
         <v>63</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>64</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>65</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>66</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>67</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>28</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>68</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="O17">
-        <v>15</v>
-      </c>
       <c r="P17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1663,37 +1753,40 @@
         <v>90</v>
       </c>
       <c r="G18" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" t="s">
         <v>70</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>71</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>72</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>73</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>74</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>34</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>75</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O18">
-        <v>15</v>
-      </c>
       <c r="P18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1710,37 +1803,40 @@
         <v>99</v>
       </c>
       <c r="G19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" t="s">
         <v>77</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>78</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>79</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>80</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>81</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>82</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>83</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="O19">
-        <v>15</v>
-      </c>
       <c r="P19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="Q19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1757,37 +1853,40 @@
         <v>101</v>
       </c>
       <c r="G20" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" t="s">
         <v>85</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>16</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>18</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>20</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>21</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>28</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>86</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>87</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>30</v>
       </c>
-      <c r="P20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="Q20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1804,37 +1903,40 @@
         <v>113</v>
       </c>
       <c r="G21" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" t="s">
         <v>103</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>30</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>35</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>40</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>45</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>28</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>104</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>30</v>
       </c>
-      <c r="P21">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="Q21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1851,34 +1953,151 @@
         <v>113</v>
       </c>
       <c r="G22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" t="s">
         <v>106</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>108</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>110</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>107</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>109</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>20</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>111</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>30</v>
       </c>
-      <c r="P22">
-        <v>15</v>
+      <c r="Q22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+      <c r="M23">
+        <v>30</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="P23">
+        <v>15</v>
+      </c>
+      <c r="Q23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" t="s">
+        <v>134</v>
+      </c>
+      <c r="M24">
+        <v>24</v>
+      </c>
+      <c r="N24" t="s">
+        <v>135</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24">
+        <v>15</v>
+      </c>
+      <c r="Q24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M25">
+        <v>7</v>
+      </c>
+      <c r="N25" t="s">
+        <v>139</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P25">
+        <v>15</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
